--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/76.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/76.xlsx
@@ -426,13 +426,13 @@
         <v>-5.025162636811599</v>
       </c>
       <c r="E2">
-        <v>-14.3171666291961</v>
+        <v>-10.30303217084294</v>
       </c>
       <c r="F2">
-        <v>-3.885275485111575</v>
+        <v>-4.209045946905142</v>
       </c>
       <c r="G2">
-        <v>-2.594498863613938</v>
+        <v>-0.5439866831358361</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.605465970444245</v>
       </c>
       <c r="E3">
-        <v>-13.92448453409498</v>
+        <v>-11.09439658910536</v>
       </c>
       <c r="F3">
-        <v>-4.365782153944354</v>
+        <v>-5.073144401075383</v>
       </c>
       <c r="G3">
-        <v>-1.000123579173238</v>
+        <v>-0.5307842275252226</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.202181581944314</v>
       </c>
       <c r="E4">
-        <v>-13.04265479058133</v>
+        <v>-13.4062595540792</v>
       </c>
       <c r="F4">
-        <v>-4.654676244068114</v>
+        <v>-4.833659559954461</v>
       </c>
       <c r="G4">
-        <v>-0.9961012663430235</v>
+        <v>-0.1161681936413599</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.855189131812396</v>
       </c>
       <c r="E5">
-        <v>-14.68201219457208</v>
+        <v>-11.60925691293343</v>
       </c>
       <c r="F5">
-        <v>-4.961805124102243</v>
+        <v>-4.920387255148713</v>
       </c>
       <c r="G5">
-        <v>-0.7859213511457744</v>
+        <v>0.806053787778954</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.551804447232997</v>
       </c>
       <c r="E6">
-        <v>-16.01247332955163</v>
+        <v>-13.58380743449794</v>
       </c>
       <c r="F6">
-        <v>-4.225783342872464</v>
+        <v>-5.049345260431116</v>
       </c>
       <c r="G6">
-        <v>-1.089097801086691</v>
+        <v>1.346007075779624</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.289897406558358</v>
       </c>
       <c r="E7">
-        <v>-16.17620483577295</v>
+        <v>-14.88843815373773</v>
       </c>
       <c r="F7">
-        <v>-4.314120875129761</v>
+        <v>-4.94955119958153</v>
       </c>
       <c r="G7">
-        <v>-1.229481484679485</v>
+        <v>-0.9191112192817329</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.055763892508589</v>
       </c>
       <c r="E8">
-        <v>-17.43982116592528</v>
+        <v>-15.4613308719741</v>
       </c>
       <c r="F8">
-        <v>-4.686568121940275</v>
+        <v>-4.834909895774699</v>
       </c>
       <c r="G8">
-        <v>0.1044101450947401</v>
+        <v>0.2488823524285347</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.832329583688004</v>
       </c>
       <c r="E9">
-        <v>-17.83729891500053</v>
+        <v>-16.55876579146694</v>
       </c>
       <c r="F9">
-        <v>-4.761930351632377</v>
+        <v>-4.977124311422289</v>
       </c>
       <c r="G9">
-        <v>-0.2273032073946936</v>
+        <v>-0.3786646599957116</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.594787709251279</v>
       </c>
       <c r="E10">
-        <v>-17.63615768500183</v>
+        <v>-18.28901419726564</v>
       </c>
       <c r="F10">
-        <v>-3.800834661259216</v>
+        <v>-4.353323931360549</v>
       </c>
       <c r="G10">
-        <v>-0.01123714222862032</v>
+        <v>1.12649142216163</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.325318325783016</v>
       </c>
       <c r="E11">
-        <v>-19.81263286256836</v>
+        <v>-18.22314301435007</v>
       </c>
       <c r="F11">
-        <v>-4.222137651855122</v>
+        <v>-4.548857765916196</v>
       </c>
       <c r="G11">
-        <v>0.4953756416460494</v>
+        <v>1.14874821982215</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.005505028168052</v>
       </c>
       <c r="E12">
-        <v>-18.80553647105453</v>
+        <v>-19.35384863237727</v>
       </c>
       <c r="F12">
-        <v>-4.294856676374356</v>
+        <v>-4.619375439212968</v>
       </c>
       <c r="G12">
-        <v>0.3417828813515627</v>
+        <v>-0.1753574373379894</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.617713493796603</v>
       </c>
       <c r="E13">
-        <v>-19.87998485648444</v>
+        <v>-17.73450255502641</v>
       </c>
       <c r="F13">
-        <v>-4.397953555910591</v>
+        <v>-4.576014363101193</v>
       </c>
       <c r="G13">
-        <v>-0.06466934723245728</v>
+        <v>0.529990705804669</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.159240435485361</v>
       </c>
       <c r="E14">
-        <v>-20.79246784055601</v>
+        <v>-19.84626583902333</v>
       </c>
       <c r="F14">
-        <v>-3.709724851796943</v>
+        <v>-4.802897656252965</v>
       </c>
       <c r="G14">
-        <v>1.13571460203404</v>
+        <v>0.8953491326097157</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.6350489141493236</v>
       </c>
       <c r="E15">
-        <v>-20.64512035329443</v>
+        <v>-21.01808547256616</v>
       </c>
       <c r="F15">
-        <v>-3.724527750988555</v>
+        <v>-3.837114988223061</v>
       </c>
       <c r="G15">
-        <v>1.489082232895846</v>
+        <v>2.790851639302523</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.05280238490323056</v>
       </c>
       <c r="E16">
-        <v>-22.45391061228217</v>
+        <v>-20.37292736611539</v>
       </c>
       <c r="F16">
-        <v>-3.769847079464771</v>
+        <v>-3.665879953528002</v>
       </c>
       <c r="G16">
-        <v>0.8006244930945492</v>
+        <v>2.275522189022952</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.5670103325416599</v>
       </c>
       <c r="E17">
-        <v>-22.64772477133646</v>
+        <v>-20.21284128147024</v>
       </c>
       <c r="F17">
-        <v>-3.062918767754572</v>
+        <v>-3.872989094619595</v>
       </c>
       <c r="G17">
-        <v>0.4158000585185879</v>
+        <v>4.488314001290589</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.198519853606076</v>
       </c>
       <c r="E18">
-        <v>-23.32247645542735</v>
+        <v>-22.06193495912624</v>
       </c>
       <c r="F18">
-        <v>-3.708130059940095</v>
+        <v>-3.343881658653811</v>
       </c>
       <c r="G18">
-        <v>1.414969049908182</v>
+        <v>2.869271842036779</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.818125788352424</v>
       </c>
       <c r="E19">
-        <v>-23.74258298911893</v>
+        <v>-24.60752605305798</v>
       </c>
       <c r="F19">
-        <v>-2.658163128416135</v>
+        <v>-3.531748772872815</v>
       </c>
       <c r="G19">
-        <v>1.585783268097957</v>
+        <v>4.986372335491781</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.40090692570905</v>
       </c>
       <c r="E20">
-        <v>-25.78372019249223</v>
+        <v>-24.81579962961876</v>
       </c>
       <c r="F20">
-        <v>-3.140578954729976</v>
+        <v>-2.681640776759567</v>
       </c>
       <c r="G20">
-        <v>2.2687653655773</v>
+        <v>2.378913836759931</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.923903713429922</v>
       </c>
       <c r="E21">
-        <v>-25.67259144034399</v>
+        <v>-27.68030850554068</v>
       </c>
       <c r="F21">
-        <v>-2.194237860518007</v>
+        <v>-3.305466496115954</v>
       </c>
       <c r="G21">
-        <v>3.117648831666139</v>
+        <v>2.866712790334922</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.37176047140577</v>
       </c>
       <c r="E22">
-        <v>-27.12793883150707</v>
+        <v>-25.26578503481294</v>
       </c>
       <c r="F22">
-        <v>-2.724497442537274</v>
+        <v>-2.657616749875308</v>
       </c>
       <c r="G22">
-        <v>2.294878948791071</v>
+        <v>3.212419818818855</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.734781555237457</v>
       </c>
       <c r="E23">
-        <v>-26.39588836579712</v>
+        <v>-27.80763560921434</v>
       </c>
       <c r="F23">
-        <v>-1.90407522195598</v>
+        <v>-2.926203770898346</v>
       </c>
       <c r="G23">
-        <v>3.113149800278269</v>
+        <v>3.215339719984492</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.005749932310725</v>
       </c>
       <c r="E24">
-        <v>-28.67714337495312</v>
+        <v>-25.92611805766342</v>
       </c>
       <c r="F24">
-        <v>-1.611615417963608</v>
+        <v>-2.254883502990888</v>
       </c>
       <c r="G24">
-        <v>1.03809654571755</v>
+        <v>2.998230832973549</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.182538203352313</v>
       </c>
       <c r="E25">
-        <v>-28.83336214279573</v>
+        <v>-27.30726640221082</v>
       </c>
       <c r="F25">
-        <v>-1.5625989280278</v>
+        <v>-1.8314282560559</v>
       </c>
       <c r="G25">
-        <v>1.40289549032646</v>
+        <v>1.10623088346129</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.268966597947427</v>
       </c>
       <c r="E26">
-        <v>-28.39096193156439</v>
+        <v>-28.9219617367558</v>
       </c>
       <c r="F26">
-        <v>-1.91999384196502</v>
+        <v>-2.667221926252449</v>
       </c>
       <c r="G26">
-        <v>0.7230484794728075</v>
+        <v>2.221368285091554</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.271744290541557</v>
       </c>
       <c r="E27">
-        <v>-29.34747979688654</v>
+        <v>-28.37426997637211</v>
       </c>
       <c r="F27">
-        <v>-1.869361180142505</v>
+        <v>-1.831514568028291</v>
       </c>
       <c r="G27">
-        <v>2.055897287402162</v>
+        <v>1.801495104891329</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.200615468740469</v>
       </c>
       <c r="E28">
-        <v>-29.30062367632918</v>
+        <v>-27.28843247881291</v>
       </c>
       <c r="F28">
-        <v>-1.921082639781885</v>
+        <v>-2.706970569171105</v>
       </c>
       <c r="G28">
-        <v>0.589064080407424</v>
+        <v>1.563473501708809</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.071595068676736</v>
       </c>
       <c r="E29">
-        <v>-30.65488647069304</v>
+        <v>-27.15949323839252</v>
       </c>
       <c r="F29">
-        <v>-2.018708607233234</v>
+        <v>-2.120855263220205</v>
       </c>
       <c r="G29">
-        <v>1.616968607077892</v>
+        <v>1.681921510558393</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.903193583099141</v>
       </c>
       <c r="E30">
-        <v>-31.28881169736778</v>
+        <v>-26.88353256083909</v>
       </c>
       <c r="F30">
-        <v>-1.19485212037431</v>
+        <v>-3.037717255522184</v>
       </c>
       <c r="G30">
-        <v>1.199459156392706</v>
+        <v>1.385942186619852</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.711663955654203</v>
       </c>
       <c r="E31">
-        <v>-29.40470612292147</v>
+        <v>-27.62620229809703</v>
       </c>
       <c r="F31">
-        <v>-1.796169419407514</v>
+        <v>-2.62976569764639</v>
       </c>
       <c r="G31">
-        <v>0.6815805860478966</v>
+        <v>2.400180781304209</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.516546294819362</v>
       </c>
       <c r="E32">
-        <v>-30.1244006473015</v>
+        <v>-25.74651425004521</v>
       </c>
       <c r="F32">
-        <v>-1.668235279999442</v>
+        <v>-2.36054756981605</v>
       </c>
       <c r="G32">
-        <v>0.7098029867701835</v>
+        <v>2.54630164031656</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.338394835160553</v>
       </c>
       <c r="E33">
-        <v>-30.41528264671019</v>
+        <v>-29.01879409646181</v>
       </c>
       <c r="F33">
-        <v>-1.783521943966814</v>
+        <v>-2.593034806349603</v>
       </c>
       <c r="G33">
-        <v>1.453182677067989</v>
+        <v>1.880557553460203</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.18876560147085</v>
       </c>
       <c r="E34">
-        <v>-31.01448353469412</v>
+        <v>-27.66555020874968</v>
       </c>
       <c r="F34">
-        <v>-1.637984121455675</v>
+        <v>-2.194667836674049</v>
       </c>
       <c r="G34">
-        <v>1.424096223959953</v>
+        <v>2.048544565759441</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.078895548936561</v>
       </c>
       <c r="E35">
-        <v>-28.60487798673872</v>
+        <v>-26.99196687095276</v>
       </c>
       <c r="F35">
-        <v>-1.863950448882407</v>
+        <v>-2.215622641494186</v>
       </c>
       <c r="G35">
-        <v>0.5257333442411662</v>
+        <v>2.310167048091425</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.020153835471369</v>
       </c>
       <c r="E36">
-        <v>-29.69148532487922</v>
+        <v>-26.34857034089097</v>
       </c>
       <c r="F36">
-        <v>-1.44953737087162</v>
+        <v>-1.669477697290104</v>
       </c>
       <c r="G36">
-        <v>2.123624428044572</v>
+        <v>2.026930013933539</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.012673282152713</v>
       </c>
       <c r="E37">
-        <v>-28.82842157765336</v>
+        <v>-28.1826204278935</v>
       </c>
       <c r="F37">
-        <v>-1.432311401629385</v>
+        <v>-2.057062797093347</v>
       </c>
       <c r="G37">
-        <v>2.00357742569952</v>
+        <v>1.460820105627088</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.054488484757797</v>
       </c>
       <c r="E38">
-        <v>-29.32852360469044</v>
+        <v>-26.1583065054587</v>
       </c>
       <c r="F38">
-        <v>-1.618628067757174</v>
+        <v>-2.479490218889214</v>
       </c>
       <c r="G38">
-        <v>1.799565056841933</v>
+        <v>3.495812448617087</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.145223413876916</v>
       </c>
       <c r="E39">
-        <v>-30.63418908024098</v>
+        <v>-27.64652156096945</v>
       </c>
       <c r="F39">
-        <v>-1.745931892210901</v>
+        <v>-1.80302211490362</v>
       </c>
       <c r="G39">
-        <v>2.060250654786304</v>
+        <v>2.570783124579471</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.275935737319926</v>
       </c>
       <c r="E40">
-        <v>-29.77265822146671</v>
+        <v>-26.4782341371526</v>
       </c>
       <c r="F40">
-        <v>-1.387579628047798</v>
+        <v>-1.948477584707156</v>
       </c>
       <c r="G40">
-        <v>1.35597181785283</v>
+        <v>3.101827734533962</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.435055118742635</v>
       </c>
       <c r="E41">
-        <v>-29.45468915478114</v>
+        <v>-24.84054774007067</v>
       </c>
       <c r="F41">
-        <v>-1.802041009089005</v>
+        <v>-2.351719201190433</v>
       </c>
       <c r="G41">
-        <v>1.494726713040303</v>
+        <v>1.426231525832782</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.614844640298503</v>
       </c>
       <c r="E42">
-        <v>-28.83789967375141</v>
+        <v>-24.23079777188588</v>
       </c>
       <c r="F42">
-        <v>-1.105903277633653</v>
+        <v>-2.181177037833378</v>
       </c>
       <c r="G42">
-        <v>1.615631146680026</v>
+        <v>2.892339723354421</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.803030762682873</v>
       </c>
       <c r="E43">
-        <v>-27.71353391933495</v>
+        <v>-25.1629116907807</v>
       </c>
       <c r="F43">
-        <v>-1.103503963171762</v>
+        <v>-1.769284427787013</v>
       </c>
       <c r="G43">
-        <v>2.050090590526281</v>
+        <v>3.830237137903183</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.985193706755412</v>
       </c>
       <c r="E44">
-        <v>-28.11204868895796</v>
+        <v>-23.6388311211292</v>
       </c>
       <c r="F44">
-        <v>-1.392592057270164</v>
+        <v>-1.600915108945942</v>
       </c>
       <c r="G44">
-        <v>1.039407521751101</v>
+        <v>3.683387958872192</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.15267225290776</v>
       </c>
       <c r="E45">
-        <v>-27.15898604930366</v>
+        <v>-24.75922993231494</v>
       </c>
       <c r="F45">
-        <v>-0.794195903797988</v>
+        <v>-1.717063308931313</v>
       </c>
       <c r="G45">
-        <v>2.331616072640363</v>
+        <v>3.120317131370792</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.295753107839955</v>
       </c>
       <c r="E46">
-        <v>-27.67417695173429</v>
+        <v>-23.26095713603315</v>
       </c>
       <c r="F46">
-        <v>-0.6296876599787578</v>
+        <v>-1.322303229478172</v>
       </c>
       <c r="G46">
-        <v>1.021487538747027</v>
+        <v>2.554442271797628</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.403251676515234</v>
       </c>
       <c r="E47">
-        <v>-27.07190349413616</v>
+        <v>-22.42774056099184</v>
       </c>
       <c r="F47">
-        <v>-1.28958861638294</v>
+        <v>-2.156278805283797</v>
       </c>
       <c r="G47">
-        <v>1.556468387347711</v>
+        <v>3.027542403178256</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.470585109074824</v>
       </c>
       <c r="E48">
-        <v>-26.91784480839521</v>
+        <v>-22.44440081686606</v>
       </c>
       <c r="F48">
-        <v>-1.505989360080417</v>
+        <v>-1.06960157063995</v>
       </c>
       <c r="G48">
-        <v>0.6676266365998685</v>
+        <v>0.2119399747558075</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.495882000316672</v>
       </c>
       <c r="E49">
-        <v>-27.41723133653907</v>
+        <v>-22.80632551650709</v>
       </c>
       <c r="F49">
-        <v>-0.9989730379290972</v>
+        <v>-2.249058632633901</v>
       </c>
       <c r="G49">
-        <v>1.672973105965743</v>
+        <v>2.544527187907511</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.475526136331034</v>
       </c>
       <c r="E50">
-        <v>-26.57301509813314</v>
+        <v>-22.34159539994393</v>
       </c>
       <c r="F50">
-        <v>-1.353658231045</v>
+        <v>-1.468876003805051</v>
       </c>
       <c r="G50">
-        <v>0.1279117078780262</v>
+        <v>1.969306658276985</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.412013187687672</v>
       </c>
       <c r="E51">
-        <v>-25.65353562171972</v>
+        <v>-22.81587153971526</v>
       </c>
       <c r="F51">
-        <v>-1.067304405209605</v>
+        <v>-1.485198468822528</v>
       </c>
       <c r="G51">
-        <v>1.800568152140333</v>
+        <v>2.440350940877725</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.312215958289858</v>
       </c>
       <c r="E52">
-        <v>-25.42314497810548</v>
+        <v>-22.32740316240389</v>
       </c>
       <c r="F52">
-        <v>-0.8646684414761703</v>
+        <v>-1.788684825251147</v>
       </c>
       <c r="G52">
-        <v>1.011287747940532</v>
+        <v>1.348797865669229</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.179401711058709</v>
       </c>
       <c r="E53">
-        <v>-25.23591069178434</v>
+        <v>-21.17921310623308</v>
       </c>
       <c r="F53">
-        <v>-1.107353952252196</v>
+        <v>-2.137469130126123</v>
       </c>
       <c r="G53">
-        <v>1.383714189471923</v>
+        <v>2.228767354371825</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.019907197267123</v>
       </c>
       <c r="E54">
-        <v>-24.65682302110548</v>
+        <v>-20.35405721492543</v>
       </c>
       <c r="F54">
-        <v>-1.141085304545141</v>
+        <v>-1.303636879705846</v>
       </c>
       <c r="G54">
-        <v>1.368558511993139</v>
+        <v>1.891906103568825</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.84495017056188</v>
       </c>
       <c r="E55">
-        <v>-24.16239970047402</v>
+        <v>-20.45800380729749</v>
       </c>
       <c r="F55">
-        <v>-0.8767750813467471</v>
+        <v>-1.751177126202837</v>
       </c>
       <c r="G55">
-        <v>-0.0435944143294569</v>
+        <v>1.504469648562379</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.659892334515014</v>
       </c>
       <c r="E56">
-        <v>-24.72958654146073</v>
+        <v>-19.29292707155208</v>
       </c>
       <c r="F56">
-        <v>-0.6914759462696277</v>
+        <v>-1.259925804586759</v>
       </c>
       <c r="G56">
-        <v>0.7202907950385946</v>
+        <v>1.286033232790187</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.469525781472697</v>
       </c>
       <c r="E57">
-        <v>-23.10705694688248</v>
+        <v>-18.58490016045282</v>
       </c>
       <c r="F57">
-        <v>-1.195164902292609</v>
+        <v>-1.710795792770962</v>
       </c>
       <c r="G57">
-        <v>0.1729417483031929</v>
+        <v>1.504893398391405</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.282280912668367</v>
       </c>
       <c r="E58">
-        <v>-24.08857651720098</v>
+        <v>-18.38734095339419</v>
       </c>
       <c r="F58">
-        <v>-0.5835479718383448</v>
+        <v>-1.600325970345398</v>
       </c>
       <c r="G58">
-        <v>0.0190477283646325</v>
+        <v>0.7490230197739293</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.100753488810995</v>
       </c>
       <c r="E59">
-        <v>-23.54004246065187</v>
+        <v>-18.77863733544897</v>
       </c>
       <c r="F59">
-        <v>-0.653695849803862</v>
+        <v>-1.731760099826591</v>
       </c>
       <c r="G59">
-        <v>1.753485573480818</v>
+        <v>0.5223201717901776</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.925472389566824</v>
       </c>
       <c r="E60">
-        <v>-23.33231682944602</v>
+        <v>-19.26739100662283</v>
       </c>
       <c r="F60">
-        <v>-0.8475145308530879</v>
+        <v>-1.102534735151514</v>
       </c>
       <c r="G60">
-        <v>0.6679113435162459</v>
+        <v>0.5529129231185826</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.761275882830331</v>
       </c>
       <c r="E61">
-        <v>-21.78425798992391</v>
+        <v>-17.83816385353599</v>
       </c>
       <c r="F61">
-        <v>-0.3831006896800471</v>
+        <v>-1.558852671684828</v>
       </c>
       <c r="G61">
-        <v>1.839814669508393</v>
+        <v>2.174441302072385</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.609706097772678</v>
       </c>
       <c r="E62">
-        <v>-23.45737063916784</v>
+        <v>-18.37763643359575</v>
       </c>
       <c r="F62">
-        <v>-0.7579725902470993</v>
+        <v>-0.91771625481973</v>
       </c>
       <c r="G62">
-        <v>1.199939185495901</v>
+        <v>1.105019223793917</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.469960786715625</v>
       </c>
       <c r="E63">
-        <v>-22.0672242167672</v>
+        <v>-16.20515084162998</v>
       </c>
       <c r="F63">
-        <v>-0.6921664420487593</v>
+        <v>-1.630459934651422</v>
       </c>
       <c r="G63">
-        <v>0.6104170991357232</v>
+        <v>0.1075253684471942</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.346123673529083</v>
       </c>
       <c r="E64">
-        <v>-21.82082088906184</v>
+        <v>-18.43844478257075</v>
       </c>
       <c r="F64">
-        <v>-0.6621203734210421</v>
+        <v>-1.690130014280392</v>
       </c>
       <c r="G64">
-        <v>-0.2575351092593181</v>
+        <v>0.3745241767349548</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.241177876107971</v>
       </c>
       <c r="E65">
-        <v>-20.63478637560893</v>
+        <v>-19.96589453688395</v>
       </c>
       <c r="F65">
-        <v>-0.7377565842365147</v>
+        <v>-1.587411640457947</v>
       </c>
       <c r="G65">
-        <v>-0.7438840438881089</v>
+        <v>-0.6285016002078903</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.155332902424536</v>
       </c>
       <c r="E66">
-        <v>-22.27558836280813</v>
+        <v>-16.86691033379288</v>
       </c>
       <c r="F66">
-        <v>-0.5365910914455653</v>
+        <v>-1.044457071820518</v>
       </c>
       <c r="G66">
-        <v>-1.095831450713568</v>
+        <v>0.408500305604495</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.093372367630329</v>
       </c>
       <c r="E67">
-        <v>-21.50227897041429</v>
+        <v>-17.48212164163093</v>
       </c>
       <c r="F67">
-        <v>-0.6654002283719173</v>
+        <v>-1.821225230695681</v>
       </c>
       <c r="G67">
-        <v>-0.4833110044920738</v>
+        <v>-0.2619149610077739</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.060158397539842</v>
       </c>
       <c r="E68">
-        <v>-20.83153951429419</v>
+        <v>-16.69579288646504</v>
       </c>
       <c r="F68">
-        <v>-1.060382818506177</v>
+        <v>-1.511643190198536</v>
       </c>
       <c r="G68">
-        <v>-0.9154894824617702</v>
+        <v>-0.4368243240296278</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.055453731038726</v>
       </c>
       <c r="E69">
-        <v>-20.87804241387895</v>
+        <v>-16.83124407250846</v>
       </c>
       <c r="F69">
-        <v>-0.4056463270922431</v>
+        <v>-1.291629221454984</v>
       </c>
       <c r="G69">
-        <v>-1.165488639405373</v>
+        <v>-0.4831388561240317</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.082633234118005</v>
       </c>
       <c r="E70">
-        <v>-20.24398812569499</v>
+        <v>-16.03121668346937</v>
       </c>
       <c r="F70">
-        <v>-0.7168675032118684</v>
+        <v>-1.32606849029213</v>
       </c>
       <c r="G70">
-        <v>-1.130830538154743</v>
+        <v>-1.454121862792271</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>2.145261879678363</v>
       </c>
       <c r="E71">
-        <v>-22.32012137619956</v>
+        <v>-16.76694879854756</v>
       </c>
       <c r="F71">
-        <v>-1.246989302816492</v>
+        <v>-1.077271458388424</v>
       </c>
       <c r="G71">
-        <v>-1.945324057181633</v>
+        <v>-1.766994900617712</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.239773460567896</v>
       </c>
       <c r="E72">
-        <v>-21.17871044561823</v>
+        <v>-16.10056120594883</v>
       </c>
       <c r="F72">
-        <v>-0.7259001699005773</v>
+        <v>-1.750808914577497</v>
       </c>
       <c r="G72">
-        <v>-0.8736110813899897</v>
+        <v>-1.771179430179351</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.366477766563793</v>
       </c>
       <c r="E73">
-        <v>-20.23088272191679</v>
+        <v>-15.79554131068818</v>
       </c>
       <c r="F73">
-        <v>-0.169980592786403</v>
+        <v>-1.398095435326316</v>
       </c>
       <c r="G73">
-        <v>-1.525083406426549</v>
+        <v>-1.108894863411532</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.526673956892899</v>
       </c>
       <c r="E74">
-        <v>-19.40031077569597</v>
+        <v>-16.46128585997783</v>
       </c>
       <c r="F74">
-        <v>-0.1972425064147776</v>
+        <v>-1.207801291791901</v>
       </c>
       <c r="G74">
-        <v>-2.135428824228742</v>
+        <v>-0.2978476222910234</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.713534376088552</v>
       </c>
       <c r="E75">
-        <v>-21.59812865126064</v>
+        <v>-17.35929131264687</v>
       </c>
       <c r="F75">
-        <v>-1.067145242765104</v>
+        <v>-2.175660990129903</v>
       </c>
       <c r="G75">
-        <v>-1.591658477221292</v>
+        <v>-1.031845226530535</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.924606061109511</v>
       </c>
       <c r="E76">
-        <v>-20.65299084111976</v>
+        <v>-17.85610566755438</v>
       </c>
       <c r="F76">
-        <v>-0.7949940915793695</v>
+        <v>-1.405416115920435</v>
       </c>
       <c r="G76">
-        <v>-1.609455970040414</v>
+        <v>0.1702701380530011</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.158854494410643</v>
       </c>
       <c r="E77">
-        <v>-21.61830753143882</v>
+        <v>-18.96059594955117</v>
       </c>
       <c r="F77">
-        <v>-0.5398661952786941</v>
+        <v>-1.89402898348139</v>
       </c>
       <c r="G77">
-        <v>-2.577823645732629</v>
+        <v>-1.202666065811389</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.408388905460971</v>
       </c>
       <c r="E78">
-        <v>-21.46755463172348</v>
+        <v>-15.83753385016131</v>
       </c>
       <c r="F78">
-        <v>-0.9088855106352397</v>
+        <v>-1.520576875267529</v>
       </c>
       <c r="G78">
-        <v>-1.485883236696039</v>
+        <v>-0.6218937513115049</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.668467210559093</v>
       </c>
       <c r="E79">
-        <v>-21.89062731589008</v>
+        <v>-18.63109059533106</v>
       </c>
       <c r="F79">
-        <v>-0.6041369405920154</v>
+        <v>-1.396091255490327</v>
       </c>
       <c r="G79">
-        <v>-2.722577249437262</v>
+        <v>-1.284737800275461</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.937537697886698</v>
       </c>
       <c r="E80">
-        <v>-22.21945792748306</v>
+        <v>-18.45998220495123</v>
       </c>
       <c r="F80">
-        <v>-0.6408907956245764</v>
+        <v>-1.676817382355208</v>
       </c>
       <c r="G80">
-        <v>-3.619185540020235</v>
+        <v>-2.196591153066777</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.208881332433984</v>
       </c>
       <c r="E81">
-        <v>-22.92278428256235</v>
+        <v>-19.43521625334709</v>
       </c>
       <c r="F81">
-        <v>-0.5411014858927368</v>
+        <v>-1.380688131756763</v>
       </c>
       <c r="G81">
-        <v>-2.472551608129345</v>
+        <v>-0.9064748669583347</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.47738982029915</v>
       </c>
       <c r="E82">
-        <v>-23.16093673062574</v>
+        <v>-20.87639404934016</v>
       </c>
       <c r="F82">
-        <v>-1.443224719092678</v>
+        <v>-2.037275975385846</v>
       </c>
       <c r="G82">
-        <v>-0.9931052226299831</v>
+        <v>-1.67869934053981</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.743554545186297</v>
       </c>
       <c r="E83">
-        <v>-22.34507326798182</v>
+        <v>-21.27237287351888</v>
       </c>
       <c r="F83">
-        <v>-1.35902699409834</v>
+        <v>-1.959064658751869</v>
       </c>
       <c r="G83">
-        <v>-2.754865000081774</v>
+        <v>-1.024224350699132</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.003739645487706</v>
       </c>
       <c r="E84">
-        <v>-24.30098911900476</v>
+        <v>-21.17234793963745</v>
       </c>
       <c r="F84">
-        <v>-1.02196765596832</v>
+        <v>-2.39467643229377</v>
       </c>
       <c r="G84">
-        <v>-1.597041424268147</v>
+        <v>-2.221387139155918</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.252277950145449</v>
       </c>
       <c r="E85">
-        <v>-25.86745620536806</v>
+        <v>-21.40493489314541</v>
       </c>
       <c r="F85">
-        <v>-1.093380914960274</v>
+        <v>-2.325619727703991</v>
       </c>
       <c r="G85">
-        <v>-2.564313309386864</v>
+        <v>0.09274047206880912</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.488984252526821</v>
       </c>
       <c r="E86">
-        <v>-24.80510337401264</v>
+        <v>-22.63600960907861</v>
       </c>
       <c r="F86">
-        <v>-1.184435294715507</v>
+        <v>-1.85055546424962</v>
       </c>
       <c r="G86">
-        <v>-2.004443779421938</v>
+        <v>-1.086293769014928</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.710124330925956</v>
       </c>
       <c r="E87">
-        <v>-27.63341162871724</v>
+        <v>-24.16125399655008</v>
       </c>
       <c r="F87">
-        <v>-1.621751135822421</v>
+        <v>-1.628291049400228</v>
       </c>
       <c r="G87">
-        <v>-3.153510962284192</v>
+        <v>-1.287389547252417</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.906564540083275</v>
       </c>
       <c r="E88">
-        <v>-27.76829675550971</v>
+        <v>-25.46943956788589</v>
       </c>
       <c r="F88">
-        <v>-0.8422122834481967</v>
+        <v>-1.779051934020486</v>
       </c>
       <c r="G88">
-        <v>-3.054836841940675</v>
+        <v>-1.413375668294921</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.073722340015412</v>
       </c>
       <c r="E89">
-        <v>-30.65543894452197</v>
+        <v>-27.66841673279653</v>
       </c>
       <c r="F89">
-        <v>-1.417750809442835</v>
+        <v>-2.028654280382193</v>
       </c>
       <c r="G89">
-        <v>-2.61765612966114</v>
+        <v>-1.841263679245722</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.205025390060226</v>
       </c>
       <c r="E90">
-        <v>-31.10491263215329</v>
+        <v>-28.96829255432827</v>
       </c>
       <c r="F90">
-        <v>-0.647974712184337</v>
+        <v>-2.708730858296116</v>
       </c>
       <c r="G90">
-        <v>-1.019765045857734</v>
+        <v>-0.563664565821264</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.28727830173353</v>
       </c>
       <c r="E91">
-        <v>-32.87660336783319</v>
+        <v>-29.31299546731813</v>
       </c>
       <c r="F91">
-        <v>-0.8234857528510829</v>
+        <v>-1.873486734052225</v>
       </c>
       <c r="G91">
-        <v>-2.793201117426534</v>
+        <v>-1.190688512050305</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.310032472932703</v>
       </c>
       <c r="E92">
-        <v>-34.61691630711395</v>
+        <v>-31.84530907545938</v>
       </c>
       <c r="F92">
-        <v>-1.006691228707991</v>
+        <v>-2.039374385723803</v>
       </c>
       <c r="G92">
-        <v>-2.792065600306564</v>
+        <v>-0.983289455106044</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.265715772830272</v>
       </c>
       <c r="E93">
-        <v>-34.84596652242191</v>
+        <v>-34.74303657246457</v>
       </c>
       <c r="F93">
-        <v>-1.460499783218292</v>
+        <v>-1.769400038318841</v>
       </c>
       <c r="G93">
-        <v>-2.397888874582161</v>
+        <v>-1.433209146620695</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.141564586054327</v>
       </c>
       <c r="E94">
-        <v>-37.86535147364317</v>
+        <v>-35.43801242147372</v>
       </c>
       <c r="F94">
-        <v>-1.344927260333183</v>
+        <v>-1.637181182556547</v>
       </c>
       <c r="G94">
-        <v>-1.786119922198082</v>
+        <v>-1.435784751050248</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.930689723566309</v>
       </c>
       <c r="E95">
-        <v>-40.16296106667787</v>
+        <v>-38.53547958577224</v>
       </c>
       <c r="F95">
-        <v>-1.378042551025022</v>
+        <v>-2.527694267690403</v>
       </c>
       <c r="G95">
-        <v>-2.637473055259218</v>
+        <v>-1.630388549485226</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.626741246539308</v>
       </c>
       <c r="E96">
-        <v>-41.43130965216821</v>
+        <v>-39.03725941242915</v>
       </c>
       <c r="F96">
-        <v>-0.8305910494407019</v>
+        <v>-2.288328996366096</v>
       </c>
       <c r="G96">
-        <v>-2.574539584557672</v>
+        <v>-3.226309858692765</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.236421735064207</v>
       </c>
       <c r="E97">
-        <v>-43.49498507067767</v>
+        <v>-42.72521468072083</v>
       </c>
       <c r="F97">
-        <v>-1.270341046539647</v>
+        <v>-1.846917691761855</v>
       </c>
       <c r="G97">
-        <v>-2.286386390273969</v>
+        <v>-1.669744314856082</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.742078571535683</v>
       </c>
       <c r="E98">
-        <v>-46.25643719937004</v>
+        <v>-43.77112688719141</v>
       </c>
       <c r="F98">
-        <v>-1.220645938619072</v>
+        <v>-2.227151228705627</v>
       </c>
       <c r="G98">
-        <v>-3.748263710596418</v>
+        <v>-1.791257888875031</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.181125191631352</v>
       </c>
       <c r="E99">
-        <v>-48.48059720823733</v>
+        <v>-45.68047643999348</v>
       </c>
       <c r="F99">
-        <v>-0.949689693546537</v>
+        <v>-2.834541248071584</v>
       </c>
       <c r="G99">
-        <v>-2.962336889027899</v>
+        <v>-3.719902266961482</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.519715280312148</v>
       </c>
       <c r="E100">
-        <v>-51.24072022980845</v>
+        <v>-47.63724817260387</v>
       </c>
       <c r="F100">
-        <v>-1.35782892057331</v>
+        <v>-2.33906935019086</v>
       </c>
       <c r="G100">
-        <v>-3.15433859866901</v>
+        <v>-2.113867241131469</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.835634406013011</v>
       </c>
       <c r="E101">
-        <v>-52.49175985552296</v>
+        <v>-51.47343284847012</v>
       </c>
       <c r="F101">
-        <v>-2.256150467723239</v>
+        <v>-2.529566208082452</v>
       </c>
       <c r="G101">
-        <v>-4.471694053474575</v>
+        <v>-3.619443762572298</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.032971398664297</v>
       </c>
       <c r="E102">
-        <v>-55.12935482375004</v>
+        <v>-52.08556252974595</v>
       </c>
       <c r="F102">
-        <v>-1.43181649353081</v>
+        <v>-1.753866258847253</v>
       </c>
       <c r="G102">
-        <v>-3.382478223416805</v>
+        <v>-2.985722582717311</v>
       </c>
     </row>
   </sheetData>
